--- a/data/file_generation/input/data_57/土超开赛时间_2025-10-27_01_00卡斯帕萨VS贝西克塔斯_比分1-1(1-1)标盘明细.xlsx
+++ b/data/file_generation/input/data_57/土超开赛时间_2025-10-27_01_00卡斯帕萨VS贝西克塔斯_比分1-1(1-1)标盘明细.xlsx
@@ -29508,26 +29508,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE448181-95CB-46D7-A0EB-FD828ED444B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A3BC34-A9FF-48A2-A9B7-11DDAEA5935E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E531709B-CF9F-4F9B-BA44-4E0BBEBFA5FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A92C13E5-4210-438D-B17C-3B63F163C270}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{446DC2DB-A9BD-4188-BCA0-7852786F0735}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7DD60A-4C9C-4022-9EF8-97FCBA46533A}"/>
 </file>